--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -1702,8 +1702,10 @@
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 (≈ 48 semanas / 11 meses) — 17 de backend + 7 de interface web</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2847,6 +2849,28 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S18 a S24</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M01 a M18 — telas web dos módulos entregues pelo backend</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
@@ -3342,23 +3366,289 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="s">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: fundação (React + TypeScript), autenticação, empresa ativa, RBAC na interface e componentes base</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+      <c r="F19" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>36.0</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: administração — empresas, filiais, usuários, perfis, alçadas e trilha de auditoria (M01/M02/M16)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+      <c r="F20" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>28.0</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: RH — funcionários, histórico funcional, verbas e reembolsos (M03)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+      <c r="F21" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G21" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: parceiros, catálogo e estoque — cadastros, movimentação e inventário (M04/M05)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+      <c r="F22" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: financeiro — contas a pagar/receber, baixas, aprovação, inadimplência e fluxo de caixa (M08/M14)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+      <c r="F23" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>37.0</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 23</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: compras, documentos fiscais e bancário — pedidos, XML, pagamentos e conciliação (M06/M07/M09/M10)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/06/2027</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/06/2027</t>
+        </is>
+      </c>
+      <c r="F24" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>32.0</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: contábil, fiscal, automação e gestão — relatórios, dashboards e integrações (M11/M12/M13/M15/M17/M18)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+      <c r="F25" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>36.0</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11">
-        <f t="shared" ref="F19:G19" si="1">SUM(F2:F18)</f>
-        <v>131</v>
-      </c>
-      <c r="G19" s="11">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11">
+        <f t="shared" ref="F26:G26" si="1">SUM(F2:F25)</f>
+        <v>170</v>
+      </c>
+      <c r="G26" s="11">
         <f t="shared" si="1"/>
-        <v>580</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>812</v>
+      </c>
+      <c r="H26" s="10"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -8988,45 +9278,2151 @@
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-001</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estruturar o projeto React + TypeScript com build, lint e testes</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G134" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-002</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementar login, renovação de sessão e recuperação de senha (RF-008/RF-009)</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G135" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-003</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selecionar a empresa ativa e enviar x-company-id em toda requisição (RF-005)</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G136" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-004</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ocultar e bloquear ações conforme as permissões do perfil (RF-011)</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G137" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-005</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padronizar layout, navegação por módulo e tratamento de erros da API</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G138" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 18</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fundação</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-006</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Criar componentes base: tabela paginada, filtros e formulários com valor decimal em string (RNF-008/RN-012)</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G139" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/04/2027</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-007</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telas de empresas e filiais (RF-001 a RF-003)</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G140" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-008</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telas de categorias, centros de custo e parâmetros (RF-006)</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G141" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-009</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telas de usuários e associação à empresa (RF-004/RF-007)</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G142" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-010</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telas de perfis e permissões por módulo (RF-010/RF-011)</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G143" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-011</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tela de alçadas de aprovação (RF-012)</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G144" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 19</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Administração</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-012</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consulta da trilha de auditoria com filtros por período e entidade (RF-117)</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G145" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/04/2027</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - RH</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-013</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cadastro de funcionários com dados profissionais e bancários (RF-013)</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G146" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RH</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - RH</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-014</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cargos, departamentos e gestores (RF-014)</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G147" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RH</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - RH</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-015</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissão, desligamento e histórico funcional (RF-015/RF-020)</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G148" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RH</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - RH</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-016</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salários, benefícios e descontos (RF-017)</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G149" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RH</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 20</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - RH</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-017</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reembolsos com upload de comprovante e fluxo de aprovação (RF-018/RF-019)</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G150" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RH</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/05/2027</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-018</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clientes e fornecedores com contatos, endereços e dados bancários (RF-022 a RF-024)</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G151" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-019</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condições e formas de pagamento (RF-026)</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G152" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-020</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catálogo de produtos e serviços com dados fiscais (RF-028 a RF-030)</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G153" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-021</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locais de estoque e consulta de saldos por local (RF-031)</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G154" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-022</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Movimentação, transferências e ajustes com justificativa (RF-032)</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G155" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 21</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Cadastros e Estoque</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-023</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventário: contagem, divergências e conclusão (RF-033)</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G156" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/05/2027</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/05/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-024</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lançamento de contas a pagar e receber com parcelamento (RF-051 a RF-053)</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G157" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-025</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação por categoria, conta contábil e centro de custo (RF-054)</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G158" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-026</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixas, estornos e encargos de atraso (RF-055/RF-057)</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G159" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-027</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fila de aprovação de títulos por alçada (RF-056)</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G160" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-028</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painel de inadimplência e aging da carteira (RF-058)</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G161" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 22</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Financeiro</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-029</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fluxo de caixa, cenários e projeções (RF-101 a RF-105)</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G162" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/05/2027</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 23</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-030</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pedidos de compra, aprovação e recebimento (RF-036 a RF-043)</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G163" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/06/2027</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 23</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-031</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentos fiscais: importação de XML e vínculo com compras (RF-044 a RF-050)</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G164" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/06/2027</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 23</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-032</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contas bancárias, pagamentos e comprovantes (RF-059 a RF-070)</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G165" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/06/2027</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 23</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-033</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conciliação bancária: importação, regras e divergências (RF-071 a RF-077)</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G166" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/06/2027</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/06/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-034</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contábil: plano de contas, lançamentos, razão e balancete (RF-078 a RF-090)</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G167" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-035</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal: parâmetros, classificações e relatórios (RF-091 a RF-100)</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G168" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-036</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validação humana do OCR de documentos (RF-118 a RF-125)</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G169" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-037</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notificações, alertas e regras de automação (M17)</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G170" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-038</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboards e relatórios com exportação PDF, XLSX e CSV (RF-106 a RF-113)</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G171" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-039</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administração de integrações e monitoramento (RF-126 a RF-131)</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G172" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contador</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
     <row r="173" ht="15.75" customHeight="1"/>
     <row r="174" ht="15.75" customHeight="1"/>
     <row r="175" ht="15.75" customHeight="1"/>
@@ -10915,6 +13311,30 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprints 18 a 24, com IDs UI-xxx. Não são requisitos novos: são as telas dos RF-001 a RF-131 já entregues pelo backend. Datadas em sequência à Sprint 17, o que pressupõe uma equipe só.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend em paralelo</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Com uma segunda equipe, as sprints de interface podem correr em paralelo às de backend, cada uma depois do módulo correspondente ficar pronto. Nesse cenário, ajuste as datas das Sprints 18 a 24.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="432">
   <si>
     <t>Planejamento de Sprints</t>
   </si>
@@ -1309,6 +1309,9 @@
   </si>
   <si>
     <t>Disponibilizar documentação da API</t>
+  </si>
+  <si>
+    <t>Concluído</t>
   </si>
 </sst>
 </file>
@@ -7098,7 +7101,7 @@
         <v>236</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>130</v>
@@ -7133,7 +7136,7 @@
         <v>236</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>130</v>
@@ -7168,7 +7171,7 @@
         <v>236</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>130</v>
@@ -7203,7 +7206,7 @@
         <v>236</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>130</v>
@@ -7238,7 +7241,7 @@
         <v>236</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>130</v>
@@ -7273,7 +7276,7 @@
         <v>236</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>130</v>
@@ -7308,7 +7311,7 @@
         <v>236</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>130</v>
@@ -7343,7 +7346,7 @@
         <v>236</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>130</v>
@@ -7378,7 +7381,7 @@
         <v>236</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>130</v>
@@ -7413,7 +7416,7 @@
         <v>236</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>130</v>
@@ -7448,7 +7451,7 @@
         <v>236</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J80" s="6" t="s">
         <v>130</v>
@@ -7483,7 +7486,7 @@
         <v>236</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J81" s="6" t="s">
         <v>130</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -7521,7 +7521,7 @@
         <v>236</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J82" s="6" t="s">
         <v>134</v>
@@ -7556,7 +7556,7 @@
         <v>236</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J83" s="6" t="s">
         <v>134</v>
@@ -7591,7 +7591,7 @@
         <v>236</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J84" s="6" t="s">
         <v>134</v>
@@ -7626,7 +7626,7 @@
         <v>236</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J85" s="6" t="s">
         <v>134</v>
@@ -7661,7 +7661,7 @@
         <v>236</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>134</v>
@@ -7696,7 +7696,7 @@
         <v>236</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J87" s="6" t="s">
         <v>134</v>
@@ -7731,7 +7731,7 @@
         <v>236</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>134</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -7766,7 +7766,7 @@
         <v>218</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>140</v>
@@ -7801,7 +7801,7 @@
         <v>218</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>140</v>
@@ -7836,7 +7836,7 @@
         <v>218</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J91" s="6" t="s">
         <v>140</v>
@@ -7871,7 +7871,7 @@
         <v>218</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>140</v>
@@ -7906,7 +7906,7 @@
         <v>218</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J93" s="6" t="s">
         <v>140</v>
@@ -7941,7 +7941,7 @@
         <v>218</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J94" s="6" t="s">
         <v>140</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -7976,7 +7976,7 @@
         <v>52</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J95" s="6" t="s">
         <v>146</v>
@@ -8011,7 +8011,7 @@
         <v>52</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J96" s="6" t="s">
         <v>146</v>
@@ -8046,7 +8046,7 @@
         <v>52</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>146</v>
@@ -8081,7 +8081,7 @@
         <v>52</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J98" s="6" t="s">
         <v>146</v>
@@ -8116,7 +8116,7 @@
         <v>52</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J99" s="6" t="s">
         <v>146</v>
@@ -8151,7 +8151,7 @@
         <v>52</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J100" s="6" t="s">
         <v>146</v>
@@ -8186,7 +8186,7 @@
         <v>52</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J101" s="6" t="s">
         <v>146</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -8221,7 +8221,7 @@
         <v>367</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J102" s="6" t="s">
         <v>152</v>
@@ -8256,7 +8256,7 @@
         <v>367</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J103" s="6" t="s">
         <v>152</v>
@@ -8291,7 +8291,7 @@
         <v>367</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J104" s="6" t="s">
         <v>152</v>
@@ -8326,7 +8326,7 @@
         <v>367</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J105" s="6" t="s">
         <v>152</v>
@@ -8361,7 +8361,7 @@
         <v>367</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>152</v>
@@ -8396,7 +8396,7 @@
         <v>367</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J107" s="6" t="s">
         <v>152</v>
@@ -8431,7 +8431,7 @@
         <v>367</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J108" s="6" t="s">
         <v>152</v>
@@ -8466,7 +8466,7 @@
         <v>367</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J109" s="6" t="s">
         <v>152</v>
@@ -8501,7 +8501,7 @@
         <v>367</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J110" s="6" t="s">
         <v>152</v>
@@ -8536,7 +8536,7 @@
         <v>367</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J111" s="6" t="s">
         <v>152</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -8571,7 +8571,7 @@
         <v>281</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J112" s="6" t="s">
         <v>158</v>
@@ -8606,7 +8606,7 @@
         <v>281</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J113" s="6" t="s">
         <v>158</v>
@@ -8641,7 +8641,7 @@
         <v>281</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J114" s="6" t="s">
         <v>158</v>
@@ -8676,7 +8676,7 @@
         <v>281</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>158</v>
@@ -8711,7 +8711,7 @@
         <v>281</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J116" s="6" t="s">
         <v>158</v>
@@ -8746,7 +8746,7 @@
         <v>281</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J117" s="6" t="s">
         <v>158</v>
@@ -8781,7 +8781,7 @@
         <v>281</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J118" s="6" t="s">
         <v>158</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -8816,7 +8816,7 @@
         <v>254</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J119" s="6" t="s">
         <v>163</v>
@@ -8851,7 +8851,7 @@
         <v>254</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J120" s="6" t="s">
         <v>163</v>
@@ -8886,7 +8886,7 @@
         <v>254</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J121" s="6" t="s">
         <v>163</v>
@@ -8921,7 +8921,7 @@
         <v>254</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J122" s="6" t="s">
         <v>163</v>
@@ -8956,7 +8956,7 @@
         <v>254</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J123" s="6" t="s">
         <v>163</v>
@@ -8991,7 +8991,7 @@
         <v>254</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J124" s="6" t="s">
         <v>163</v>
@@ -9026,7 +9026,7 @@
         <v>254</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J125" s="6" t="s">
         <v>163</v>
@@ -9061,7 +9061,7 @@
         <v>254</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J126" s="6" t="s">
         <v>163</v>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -1701,13 +1701,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 (≈ 48 semanas / 11 meses) — 17 de backend + 7 de interface web</t>
+          <t xml:space="preserve">32 (≈ 64 semanas / 15 meses) — 17 de backend + 15 de interface web</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>39</v>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum — backlog organizado pelas 8 fases do Roadmap de Implementação (seção 14 da ERS), acrescidas da Fase 9 (interface web por módulo) e da Fase 10 (qualidade e entrega da interface)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1874,8 +1876,50 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S18 a S29</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M01 a M18 — telas web dos módulos entregues pelo backend</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S30 a S32</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design system, acessibilidade, responsividade, testes E2E, performance, segurança do front e go-live</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2852,28 +2896,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fase 9 - Interface Web</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S18 a S24</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M01 a M18 — telas web dos módulos entregues pelo backend</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alta</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
@@ -3572,7 +3594,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend: compras, documentos fiscais e bancário — pedidos, XML, pagamentos e conciliação (M06/M07/M09/M10)</t>
+          <t xml:space="preserve">Frontend: compras — pedidos, aprovação, recebimento, divergências e histórico de preços (M06)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -3586,10 +3608,10 @@
         </is>
       </c>
       <c r="F24" s="6">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G24" s="6">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -3610,7 +3632,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend: contábil, fiscal, automação e gestão — relatórios, dashboards e integrações (M11/M12/M13/M15/M17/M18)</t>
+          <t xml:space="preserve">Frontend: documentos fiscais — importação de XML, processamento, vínculos, anexos e reprocessamento (M07)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -3627,46 +3649,331 @@
         <v>6.0</v>
       </c>
       <c r="G25" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: bancário — contas, pagamentos PIX/boleto/transferência, agendamento, comprovantes e extratos (M09)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+      <c r="F26" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G26" s="6">
         <v>36.0</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: conciliação bancária — importação, sugestões, conciliação manual, regras, divergências e histórico (M10)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+      <c r="F27" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: contabilidade — plano de contas, lançamentos, razão, balancete, DRE e fechamento de períodos (M11)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+      <c r="F28" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>39.0</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Baixa</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="11">
-        <f t="shared" ref="F26:G26" si="1">SUM(F2:F25)</f>
-        <v>170</v>
-      </c>
-      <c r="G26" s="11">
-        <f t="shared" si="1"/>
-        <v>812</v>
-      </c>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: fiscal — parâmetros, classificações, regras e relatórios; notificações e regras de automação (M12/M17)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+      <c r="F29" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>38.0</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend: dashboards, relatórios, exportação e administração das integrações externas (M15/M18)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+      <c r="F30" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>36.0</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interface: biblioteca de componentes, temas e recursos transversais — busca global, preferências, onboarding e impressão</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+      <c r="F31" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>31.0</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interface: acessibilidade WCAG 2.1 AA, responsividade em tablet e celular, formatos pt-BR e performance (RNF-014)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+      <c r="F32" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G32" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interface: testes E2E, isolamento multiempresa, hardening, observabilidade, pipeline, documentação e go-live</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+      <c r="F33" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="G33" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="B34" s="6">
+        <v>224.0</v>
+      </c>
+      <c r="G34" s="6">
+        <v>1089.0</v>
+      </c>
+    </row>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
@@ -5115,7 +5422,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="A14" s="6" t="s">
         <v>55</v>
       </c>
@@ -5150,7 +5457,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" hidden="1">
+    <row r="15">
       <c r="A15" s="6" t="s">
         <v>55</v>
       </c>
@@ -5185,7 +5492,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16">
       <c r="A16" s="6" t="s">
         <v>55</v>
       </c>
@@ -5220,7 +5527,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17">
       <c r="A17" s="6" t="s">
         <v>55</v>
       </c>
@@ -5255,7 +5562,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="A18" s="6" t="s">
         <v>55</v>
       </c>
@@ -5290,7 +5597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="6" t="s">
         <v>74</v>
       </c>
@@ -5325,7 +5632,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="A20" s="6" t="s">
         <v>74</v>
       </c>
@@ -5360,7 +5667,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>74</v>
       </c>
@@ -5395,7 +5702,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>74</v>
       </c>
@@ -5430,7 +5737,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>74</v>
       </c>
@@ -5465,7 +5772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
         <v>74</v>
       </c>
@@ -5500,7 +5807,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" ht="15.75" hidden="1" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
         <v>74</v>
       </c>
@@ -5535,7 +5842,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>74</v>
       </c>
@@ -5570,7 +5877,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
         <v>74</v>
       </c>
@@ -5605,7 +5912,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
         <v>86</v>
       </c>
@@ -5640,7 +5947,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" ht="15.75" hidden="1" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
         <v>86</v>
       </c>
@@ -5675,7 +5982,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>86</v>
       </c>
@@ -5710,7 +6017,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>86</v>
       </c>
@@ -5745,7 +6052,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>86</v>
       </c>
@@ -5780,7 +6087,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>86</v>
       </c>
@@ -5815,7 +6122,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" ht="15.75" hidden="1" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>86</v>
       </c>
@@ -5850,7 +6157,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" ht="15.75" hidden="1" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
         <v>86</v>
       </c>
@@ -5885,7 +6192,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" ht="15.75" hidden="1" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>86</v>
       </c>
@@ -5920,7 +6227,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>96</v>
       </c>
@@ -5955,7 +6262,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" ht="15.75" hidden="1" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>96</v>
       </c>
@@ -5990,7 +6297,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" ht="15.75" hidden="1" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>96</v>
       </c>
@@ -6025,7 +6332,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" ht="15.75" hidden="1" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>96</v>
       </c>
@@ -6060,7 +6367,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" ht="15.75" hidden="1" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>96</v>
       </c>
@@ -6095,7 +6402,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="42" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>104</v>
       </c>
@@ -6130,7 +6437,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>104</v>
       </c>
@@ -6165,7 +6472,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="6" t="s">
         <v>104</v>
       </c>
@@ -6200,7 +6507,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="6" t="s">
         <v>104</v>
       </c>
@@ -6235,7 +6542,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>104</v>
       </c>
@@ -6270,7 +6577,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="47" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6" t="s">
         <v>104</v>
       </c>
@@ -6305,7 +6612,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>104</v>
       </c>
@@ -6340,7 +6647,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="6" t="s">
         <v>104</v>
       </c>
@@ -6375,7 +6682,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" ht="15.75" hidden="1" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>109</v>
       </c>
@@ -6410,7 +6717,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" ht="15.75" hidden="1" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="6" t="s">
         <v>109</v>
       </c>
@@ -6445,7 +6752,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" ht="15.75" hidden="1" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="6" t="s">
         <v>109</v>
       </c>
@@ -6480,7 +6787,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="6" t="s">
         <v>109</v>
       </c>
@@ -6515,7 +6822,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" ht="15.75" hidden="1" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="6" t="s">
         <v>109</v>
       </c>
@@ -6550,7 +6857,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="6" t="s">
         <v>115</v>
       </c>
@@ -6585,7 +6892,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>115</v>
       </c>
@@ -6620,7 +6927,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="57" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="6" t="s">
         <v>115</v>
       </c>
@@ -6655,7 +6962,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="58" ht="15.75" hidden="1" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6" t="s">
         <v>115</v>
       </c>
@@ -6690,7 +6997,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6" t="s">
         <v>115</v>
       </c>
@@ -6725,7 +7032,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6" t="s">
         <v>115</v>
       </c>
@@ -6760,7 +7067,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="6" t="s">
         <v>115</v>
       </c>
@@ -6795,7 +7102,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" ht="15.75" hidden="1" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6" t="s">
         <v>122</v>
       </c>
@@ -6830,7 +7137,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="15.75" hidden="1" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6" t="s">
         <v>122</v>
       </c>
@@ -6865,7 +7172,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="6" t="s">
         <v>122</v>
       </c>
@@ -6900,7 +7207,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" ht="15.75" hidden="1" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6" t="s">
         <v>122</v>
       </c>
@@ -6935,7 +7242,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" ht="15.75" hidden="1" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6" t="s">
         <v>122</v>
       </c>
@@ -6970,7 +7277,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6" t="s">
         <v>122</v>
       </c>
@@ -7005,7 +7312,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6" t="s">
         <v>122</v>
       </c>
@@ -7040,7 +7347,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" ht="15.75" hidden="1" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6" t="s">
         <v>122</v>
       </c>
@@ -7075,7 +7382,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" ht="15.75" hidden="1" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6" t="s">
         <v>126</v>
       </c>
@@ -7110,7 +7417,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="71" ht="15.75" hidden="1" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
         <v>126</v>
       </c>
@@ -7145,7 +7452,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="72" ht="15.75" hidden="1" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6" t="s">
         <v>126</v>
       </c>
@@ -7180,7 +7487,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6" t="s">
         <v>126</v>
       </c>
@@ -7215,7 +7522,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>126</v>
       </c>
@@ -7250,7 +7557,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
         <v>126</v>
       </c>
@@ -7285,7 +7592,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="76" ht="15.75" hidden="1" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
         <v>126</v>
       </c>
@@ -7320,7 +7627,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="77" ht="15.75" hidden="1" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6" t="s">
         <v>126</v>
       </c>
@@ -7355,7 +7662,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="78" ht="15.75" hidden="1" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
         <v>126</v>
       </c>
@@ -7390,7 +7697,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="79" ht="15.75" hidden="1" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
         <v>126</v>
       </c>
@@ -7425,7 +7732,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="80" ht="15.75" hidden="1" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
         <v>126</v>
       </c>
@@ -7460,7 +7767,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="81" ht="15.75" hidden="1" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
         <v>126</v>
       </c>
@@ -7495,7 +7802,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="82" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
         <v>132</v>
       </c>
@@ -7530,7 +7837,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="83" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
         <v>132</v>
       </c>
@@ -7565,7 +7872,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="84" ht="15.75" hidden="1" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>132</v>
       </c>
@@ -7600,7 +7907,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" ht="15.75" hidden="1" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
         <v>132</v>
       </c>
@@ -7635,7 +7942,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="86" ht="15.75" hidden="1" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
         <v>132</v>
       </c>
@@ -7670,7 +7977,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="87" ht="15.75" hidden="1" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
         <v>132</v>
       </c>
@@ -7705,7 +8012,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="88" ht="15.75" hidden="1" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
         <v>132</v>
       </c>
@@ -7740,7 +8047,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
         <v>138</v>
       </c>
@@ -7766,7 +8073,7 @@
         <v>218</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>140</v>
@@ -7775,7 +8082,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="90" ht="15.75" hidden="1" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
         <v>138</v>
       </c>
@@ -7801,7 +8108,7 @@
         <v>218</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>140</v>
@@ -7810,7 +8117,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
         <v>138</v>
       </c>
@@ -7836,7 +8143,7 @@
         <v>218</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J91" s="6" t="s">
         <v>140</v>
@@ -7845,7 +8152,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
         <v>138</v>
       </c>
@@ -7871,7 +8178,7 @@
         <v>218</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>140</v>
@@ -7880,7 +8187,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
         <v>138</v>
       </c>
@@ -7906,7 +8213,7 @@
         <v>218</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J93" s="6" t="s">
         <v>140</v>
@@ -7915,7 +8222,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="94" ht="15.75" hidden="1" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
         <v>138</v>
       </c>
@@ -7941,7 +8248,7 @@
         <v>218</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J94" s="6" t="s">
         <v>140</v>
@@ -7950,7 +8257,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="95" ht="15.75" hidden="1" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
         <v>144</v>
       </c>
@@ -7976,7 +8283,7 @@
         <v>52</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J95" s="6" t="s">
         <v>146</v>
@@ -7985,7 +8292,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="96" ht="15.75" hidden="1" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
         <v>144</v>
       </c>
@@ -8011,7 +8318,7 @@
         <v>52</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J96" s="6" t="s">
         <v>146</v>
@@ -8020,7 +8327,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="97" ht="15.75" hidden="1" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
         <v>144</v>
       </c>
@@ -8046,7 +8353,7 @@
         <v>52</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>146</v>
@@ -8055,7 +8362,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="98" ht="15.75" hidden="1" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>144</v>
       </c>
@@ -8081,7 +8388,7 @@
         <v>52</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J98" s="6" t="s">
         <v>146</v>
@@ -8090,7 +8397,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="99" ht="15.75" hidden="1" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
         <v>144</v>
       </c>
@@ -8116,7 +8423,7 @@
         <v>52</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J99" s="6" t="s">
         <v>146</v>
@@ -8125,7 +8432,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="100" ht="15.75" hidden="1" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
         <v>144</v>
       </c>
@@ -8151,7 +8458,7 @@
         <v>52</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J100" s="6" t="s">
         <v>146</v>
@@ -8160,7 +8467,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="101" ht="15.75" hidden="1" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
         <v>144</v>
       </c>
@@ -8186,7 +8493,7 @@
         <v>52</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J101" s="6" t="s">
         <v>146</v>
@@ -8195,7 +8502,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="102" ht="15.75" hidden="1" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
         <v>148</v>
       </c>
@@ -8221,7 +8528,7 @@
         <v>367</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J102" s="6" t="s">
         <v>152</v>
@@ -8230,7 +8537,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="103" ht="15.75" hidden="1" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
         <v>148</v>
       </c>
@@ -8256,7 +8563,7 @@
         <v>367</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J103" s="6" t="s">
         <v>152</v>
@@ -8265,7 +8572,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
         <v>148</v>
       </c>
@@ -8291,7 +8598,7 @@
         <v>367</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J104" s="6" t="s">
         <v>152</v>
@@ -8300,7 +8607,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
         <v>148</v>
       </c>
@@ -8326,7 +8633,7 @@
         <v>367</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J105" s="6" t="s">
         <v>152</v>
@@ -8335,7 +8642,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="106" ht="15.75" hidden="1" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
         <v>148</v>
       </c>
@@ -8361,7 +8668,7 @@
         <v>367</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>152</v>
@@ -8370,7 +8677,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="107" ht="15.75" hidden="1" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
         <v>148</v>
       </c>
@@ -8396,7 +8703,7 @@
         <v>367</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J107" s="6" t="s">
         <v>152</v>
@@ -8405,7 +8712,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="108" ht="15.75" hidden="1" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
         <v>148</v>
       </c>
@@ -8431,7 +8738,7 @@
         <v>367</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J108" s="6" t="s">
         <v>152</v>
@@ -8440,7 +8747,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="109" ht="15.75" hidden="1" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
         <v>148</v>
       </c>
@@ -8466,7 +8773,7 @@
         <v>367</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J109" s="6" t="s">
         <v>152</v>
@@ -8475,7 +8782,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="110" ht="15.75" hidden="1" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
         <v>148</v>
       </c>
@@ -8501,7 +8808,7 @@
         <v>367</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J110" s="6" t="s">
         <v>152</v>
@@ -8510,7 +8817,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="111" ht="15.75" hidden="1" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
         <v>148</v>
       </c>
@@ -8536,7 +8843,7 @@
         <v>367</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J111" s="6" t="s">
         <v>152</v>
@@ -8545,7 +8852,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="112" ht="15.75" hidden="1" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
         <v>155</v>
       </c>
@@ -8571,7 +8878,7 @@
         <v>281</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J112" s="6" t="s">
         <v>158</v>
@@ -8580,7 +8887,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="113" ht="15.75" hidden="1" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
         <v>155</v>
       </c>
@@ -8606,7 +8913,7 @@
         <v>281</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J113" s="6" t="s">
         <v>158</v>
@@ -8615,7 +8922,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="114" ht="15.75" hidden="1" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
         <v>155</v>
       </c>
@@ -8641,7 +8948,7 @@
         <v>281</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J114" s="6" t="s">
         <v>158</v>
@@ -8650,7 +8957,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="115" ht="15.75" hidden="1" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
         <v>155</v>
       </c>
@@ -8676,7 +8983,7 @@
         <v>281</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>158</v>
@@ -8685,7 +8992,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="116" ht="15.75" hidden="1" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
         <v>155</v>
       </c>
@@ -8711,7 +9018,7 @@
         <v>281</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J116" s="6" t="s">
         <v>158</v>
@@ -8720,7 +9027,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="117" ht="15.75" hidden="1" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
         <v>155</v>
       </c>
@@ -8746,7 +9053,7 @@
         <v>281</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J117" s="6" t="s">
         <v>158</v>
@@ -8755,7 +9062,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="118" ht="15.75" hidden="1" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
         <v>155</v>
       </c>
@@ -8781,7 +9088,7 @@
         <v>281</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J118" s="6" t="s">
         <v>158</v>
@@ -8790,7 +9097,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="119" ht="15.75" hidden="1" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
         <v>160</v>
       </c>
@@ -8816,7 +9123,7 @@
         <v>254</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J119" s="6" t="s">
         <v>163</v>
@@ -8825,7 +9132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" ht="15.75" hidden="1" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
         <v>160</v>
       </c>
@@ -8851,7 +9158,7 @@
         <v>254</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J120" s="6" t="s">
         <v>163</v>
@@ -8860,7 +9167,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" ht="15.75" hidden="1" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
         <v>160</v>
       </c>
@@ -8886,7 +9193,7 @@
         <v>254</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J121" s="6" t="s">
         <v>163</v>
@@ -8895,7 +9202,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" ht="15.75" hidden="1" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
         <v>160</v>
       </c>
@@ -8921,7 +9228,7 @@
         <v>254</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J122" s="6" t="s">
         <v>163</v>
@@ -8930,7 +9237,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" ht="15.75" hidden="1" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
         <v>160</v>
       </c>
@@ -8956,7 +9263,7 @@
         <v>254</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J123" s="6" t="s">
         <v>163</v>
@@ -8965,7 +9272,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" ht="15.75" hidden="1" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
         <v>160</v>
       </c>
@@ -8991,7 +9298,7 @@
         <v>254</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J124" s="6" t="s">
         <v>163</v>
@@ -9000,7 +9307,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" ht="15.75" hidden="1" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
         <v>160</v>
       </c>
@@ -9026,7 +9333,7 @@
         <v>254</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J125" s="6" t="s">
         <v>163</v>
@@ -9035,7 +9342,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" ht="15.75" hidden="1" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
         <v>160</v>
       </c>
@@ -9061,7 +9368,7 @@
         <v>254</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>431</v>
+        <v>54</v>
       </c>
       <c r="J126" s="6" t="s">
         <v>163</v>
@@ -9070,7 +9377,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" ht="15.75" hidden="1" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
         <v>168</v>
       </c>
@@ -9096,7 +9403,7 @@
         <v>52</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J127" s="6" t="s">
         <v>170</v>
@@ -9105,7 +9412,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="128" ht="15.75" hidden="1" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
         <v>168</v>
       </c>
@@ -9131,7 +9438,7 @@
         <v>52</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J128" s="6" t="s">
         <v>170</v>
@@ -9140,7 +9447,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="129" ht="15.75" hidden="1" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
         <v>168</v>
       </c>
@@ -9166,7 +9473,7 @@
         <v>52</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J129" s="6" t="s">
         <v>170</v>
@@ -9175,7 +9482,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="130" ht="15.75" hidden="1" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
         <v>168</v>
       </c>
@@ -9201,7 +9508,7 @@
         <v>52</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J130" s="6" t="s">
         <v>170</v>
@@ -9210,7 +9517,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="131" ht="15.75" hidden="1" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
         <v>168</v>
       </c>
@@ -9236,7 +9543,7 @@
         <v>52</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J131" s="6" t="s">
         <v>170</v>
@@ -9245,7 +9552,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
         <v>168</v>
       </c>
@@ -9271,7 +9578,7 @@
         <v>52</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="J132" s="6" t="s">
         <v>170</v>
@@ -10889,7 +11196,7 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -10899,7 +11206,7 @@
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedidos de compra, aprovação e recebimento (RF-036 a RF-043)</t>
+          <t xml:space="preserve">Pedidos de compra: criação, itens, quantidades, preços, descontos e frete (RF-036/RF-037)</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
@@ -10944,7 +11251,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -10954,7 +11261,7 @@
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos fiscais: importação de XML e vínculo com compras (RF-044 a RF-050)</t>
+          <t xml:space="preserve">Acompanhamento do pedido e submissão à aprovação por alçada (RF-036/RF-038)</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -10963,7 +11270,7 @@
         </is>
       </c>
       <c r="G164" s="6">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
@@ -10999,7 +11306,7 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -11009,7 +11316,7 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contas bancárias, pagamentos e comprovantes (RF-059 a RF-070)</t>
+          <t xml:space="preserve">Recebimento total ou parcial com conferência de quantidade e preço (RF-039/RF-040)</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
@@ -11054,7 +11361,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Compras e Bancário</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -11064,7 +11371,7 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conciliação bancária: importação, regras e divergências (RF-071 a RF-077)</t>
+          <t xml:space="preserve">Tratamento de divergências de recebimento e justificativa (RF-040)</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -11073,7 +11380,7 @@
         </is>
       </c>
       <c r="G166" s="6">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
@@ -11099,7 +11406,7 @@
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 24</t>
+          <t xml:space="preserve">Sprint 23</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -11109,7 +11416,7 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
@@ -11119,20 +11426,20 @@
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contábil: plano de contas, lançamentos, razão e balancete (RF-078 a RF-090)</t>
+          <t xml:space="preserve">Vínculos do pedido com fornecedor, NF, estoque e financeiro (RF-041)</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baixa</t>
+          <t xml:space="preserve">Média</t>
         </is>
       </c>
       <c r="G167" s="6">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contador</t>
+          <t xml:space="preserve">Compras</t>
         </is>
       </c>
       <c r="I167" s="6" t="inlineStr">
@@ -11142,19 +11449,19 @@
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/06/2027</t>
+          <t xml:space="preserve">14/06/2027</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/07/2027</t>
+          <t xml:space="preserve">27/06/2027</t>
         </is>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 24</t>
+          <t xml:space="preserve">Sprint 23</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -11164,7 +11471,7 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Compras</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -11174,20 +11481,20 @@
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiscal: parâmetros, classificações e relatórios (RF-091 a RF-100)</t>
+          <t xml:space="preserve">Histórico de compras e evolução de preços por produto e fornecedor (RF-042)</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baixa</t>
+          <t xml:space="preserve">Média</t>
         </is>
       </c>
       <c r="G168" s="6">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contador</t>
+          <t xml:space="preserve">Compras</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
@@ -11197,12 +11504,12 @@
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/06/2027</t>
+          <t xml:space="preserve">14/06/2027</t>
         </is>
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/07/2027</t>
+          <t xml:space="preserve">27/06/2027</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11526,7 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
@@ -11229,20 +11536,20 @@
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validação humana do OCR de documentos (RF-118 a RF-125)</t>
+          <t xml:space="preserve">Importação de XML com fila de processamento e situação por documento (RF-043/RF-049)</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baixa</t>
+          <t xml:space="preserve">Média</t>
         </is>
       </c>
       <c r="G169" s="6">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contador</t>
+          <t xml:space="preserve">Fiscal</t>
         </is>
       </c>
       <c r="I169" s="6" t="inlineStr">
@@ -11274,7 +11581,7 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -11284,12 +11591,12 @@
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificações, alertas e regras de automação (M17)</t>
+          <t xml:space="preserve">Detalhe do documento: chave, emitente, destinatário, itens, valores e tributos (RF-045)</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baixa</t>
+          <t xml:space="preserve">Média</t>
         </is>
       </c>
       <c r="G170" s="6">
@@ -11297,7 +11604,7 @@
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contador</t>
+          <t xml:space="preserve">Fiscal</t>
         </is>
       </c>
       <c r="I170" s="6" t="inlineStr">
@@ -11329,7 +11636,7 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -11339,20 +11646,20 @@
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dashboards e relatórios com exportação PDF, XLSX e CSV (RF-106 a RF-113)</t>
+          <t xml:space="preserve">Alerta de documento duplicado e resolução pelo usuário (RF-046)</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baixa</t>
+          <t xml:space="preserve">Média</t>
         </is>
       </c>
       <c r="G171" s="6">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contador</t>
+          <t xml:space="preserve">Fiscal</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
@@ -11384,7 +11691,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frontend - Contábil e Gestão</t>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -11394,92 +11701,3008 @@
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administração de integrações e monitoramento (RF-126 a RF-131)</t>
+          <t xml:space="preserve">Vínculo do documento com fornecedor, pedido, produtos, estoque e títulos (RF-047)</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G172" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-040</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anexos: DANFE/PDF, documento original e metadados (RF-044/RF-048)</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G173" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 24</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Documentos Fiscais</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-041</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reprocessamento de documentos com erro e acompanhamento da coleta automática (RF-049/RF-050)</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G174" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/06/2027</t>
+        </is>
+      </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-042</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contas bancárias da empresa: cadastro, saldo informado pelo banco e situação (RF-059)</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G175" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-043</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emissão de pagamento PIX, boleto e transferência com Idempotency-Key (RF-062/RF-067)</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G176" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-044</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agendamento, consulta e cancelamento de ordens quando suportado (RF-063 a RF-065)</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G177" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-045</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acompanhamento de status, identificador externo e comprovante da ordem (RF-068)</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G178" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-046</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importação e consulta de extratos bancários (RF-060)</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G179" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 25</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Bancário</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-047</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painel de operações assíncronas: fila, tentativas e reprocessamento (RF-069/RF-070)</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G180" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/07/2027</t>
+        </is>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/07/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-048</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importação de OFX/CSV e listagem de movimentos identificados (RF-071/RF-072)</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G181" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-049</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tela de sugestões de correspondência com score e critério aplicado (RF-073)</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G182" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-050</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conciliação manual: vincular, justificar divergência e desfazer (RF-074)</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G183" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-051</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cadastro de regras de conciliação automática, prioridade e tolerâncias (RF-075)</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G184" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-052</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painel de divergências entre extrato e lançamentos (RF-076)</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G185" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 26</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Conciliação Bancária</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-053</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Histórico de conciliações e trilha de desfazimento (RF-077)</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Média</t>
+        </is>
+      </c>
+      <c r="G186" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financeiro</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/07/2027</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-054</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plano de contas em árvore com contas patrimoniais e de resultado (RF-078/RF-079)</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Baixa</t>
         </is>
       </c>
-      <c r="G172" s="6">
+      <c r="G187" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-055</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação contábil das operações financeiras (RF-080)</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G188" s="6">
         <v>5.0</v>
       </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contador</t>
-        </is>
-      </c>
-      <c r="I172" s="6" t="inlineStr">
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">A Fazer</t>
         </is>
       </c>
-      <c r="J172" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28/06/2027</t>
-        </is>
-      </c>
-      <c r="K172" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11/07/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
+      <c r="J188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-056</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lançamentos de débito e crédito com partida dobrada, origem e documento (RF-081/RF-082)</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G189" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-057</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Razão e balancete com filtros por período, conta e centro de custo (RF-083/RF-084)</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G190" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-058</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRE por período com comparativo entre exercícios (RF-085)</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G191" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-059</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fechamento e reabertura de períodos com bloqueio visível na interface (RF-086)</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G192" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 27</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Contabilidade</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-060</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exportação de dados contábeis para sistemas externos (RF-087)</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G193" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09/08/2027</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/08/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-061</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parâmetros fiscais da empresa e classificações fiscais (RF-088/RF-089)</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G194" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-062</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regras fiscais associadas a operações e produtos (RF-091)</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G195" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-063</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Informações tributárias e eventos do documento fiscal (RF-090/RF-092)</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G196" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-064</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relatórios fiscais e acompanhamento das integrações fiscais (RF-093/RF-094)</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G197" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-065</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central de notificações in-app com prioridade, leitura e link para a entidade (RF-119)</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G198" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-066</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferências de alerta: vencimento, pagamento, aprovação pendente e divergência (RF-120 a RF-124)</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G199" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 28</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Fiscal e Automação</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-067</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Editor de regras de automação com condições, ações e histórico de execução (RF-125)</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G200" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23/08/2027</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-068</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboard financeiro com indicadores do período e comparativos (RF-106)</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G201" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-069</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painéis de contas a pagar/receber, fluxo de caixa e resultado (RF-107/RF-108)</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G202" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-070</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicadores de compras, estoque e fornecedores (RF-109)</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G203" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-071</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicadores de funcionários e centros de custo (RF-110)</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G204" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-072</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filtros combinados por período, empresa, filial, categoria, conta e centro de custo (RF-112)</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G205" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-073</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relatórios contábeis e fiscais com exportação PDF, XLSX e CSV (RF-111/RF-113)</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G206" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-074</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administração de integrações: provedores, credenciais e parâmetros (RF-126/RF-127)</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G207" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 29</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 9 - Interface Web</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Dashboards e Integrações</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-075</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitoramento de integrações, log de erros e reprocessamento (RF-128 a RF-130)</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixa</t>
+        </is>
+      </c>
+      <c r="G208" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretor/Gestor</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06/09/2027</t>
+        </is>
+      </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19/09/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-076</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biblioteca de componentes com tokens de design, tema claro/escuro e documentação viva</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G209" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-077</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Busca global por entidade com atalho de teclado e navegação por resultado</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G210" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-078</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preferências do usuário: tema, densidade, colunas visíveis e filtros salvos</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G211" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-079</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Onboarding da empresa e assistente de primeira configuração (RF-006)</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G212" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-080</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Layout de impressão e exportação de listas e telas de detalhe (RF-113)</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G213" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 30</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Design System e Transversais</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-081</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padronização de estados vazios, carregamento, erro e confirmação de ação</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G214" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/09/2027</t>
+        </is>
+      </c>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Acessibilidade e Performance</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-082</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acessibilidade WCAG 2.1 AA: navegação por teclado, ordem de foco e leitores de tela</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G215" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Acessibilidade e Performance</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-083</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Responsividade e uso em tablet e celular nas telas operacionais (RNF-014)</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G216" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="K216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Acessibilidade e Performance</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-084</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formatos pt-BR de moeda, data e número preservando o decimal como string (RN-012)</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G217" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Acessibilidade e Performance</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-085</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Performance: code splitting, cache de consultas e listas virtualizadas (RNF-008)</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G218" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 31</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Acessibilidade e Performance</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-086</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auditoria de acessibilidade e responsividade sobre as telas já entregues</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G219" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04/10/2027</t>
+        </is>
+      </c>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-087</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testes E2E dos fluxos críticos: login, pagamento, baixa e conciliação (RNF-012)</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G220" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-088</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testes de isolamento multiempresa na interface: troca de empresa e permissões (RF-005/RNF-004)</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G221" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-089</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardening do front: CSP, sanitização de conteúdo, expiração e renovação de sessão (RNF-002)</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G222" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-090</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observabilidade: captura de erros do cliente e correlation id nas requisições (RNF-010)</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G223" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-091</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipeline de build, testes e publicação da interface</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G224" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-092</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual do usuário e ajuda contextual por módulo</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G225" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 32</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase 10 - Qualidade e Entrega da Interface</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend - Qualidade, Segurança e Go-live</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-093</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Homologação assistida (UAT), correção dos apontamentos e go-live</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+      <c r="G226" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrador</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Fazer</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/10/2027</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31/10/2027</t>
+        </is>
+      </c>
+    </row>
     <row r="227" ht="15.75" customHeight="1"/>
     <row r="228" ht="15.75" customHeight="1"/>
     <row r="229" ht="15.75" customHeight="1"/>
@@ -12255,13 +15478,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$K$132">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Sprint 1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$K$226"/>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -9629,7 +9629,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -9959,7 +9959,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J148" s="6" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J150" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -10564,7 +10564,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J152" s="6" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J153" s="6" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J156" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J158" s="6" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J160" s="6" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J162" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -11224,7 +11224,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J164" s="6" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J166" s="6" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J168" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -11554,7 +11554,7 @@
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J170" s="6" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J171" s="6" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J172" s="6" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J174" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -11884,7 +11884,7 @@
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J175" s="6" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J176" s="6" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J177" s="6" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J178" s="6" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J179" s="6" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -12214,7 +12214,7 @@
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J181" s="6" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J182" s="6" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J184" s="6" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J185" s="6" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J186" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -12544,7 +12544,7 @@
       </c>
       <c r="I187" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J187" s="6" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J188" s="6" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J189" s="6" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="I191" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J191" s="6" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J192" s="6" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="I193" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J193" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -12929,7 +12929,7 @@
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J194" s="6" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="I196" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J196" s="6" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="I197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J197" s="6" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="I198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J198" s="6" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J199" s="6" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J200" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -13314,7 +13314,7 @@
       </c>
       <c r="I201" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J201" s="6" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J202" s="6" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J203" s="6" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J204" s="6" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J205" s="6" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J206" s="6" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="I207" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J207" s="6" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="I208" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J208" s="6" t="inlineStr">

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -13752,10 +13752,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I209" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I209" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
@@ -13807,10 +13805,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I210" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I210" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
@@ -13862,10 +13858,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I211" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I211" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
@@ -13917,10 +13911,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I212" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
@@ -13972,10 +13964,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I213" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J213" s="6" t="inlineStr">
         <is>
@@ -14027,10 +14017,8 @@
           <t xml:space="preserve">Administrador</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Fazer</t>
-        </is>
+      <c r="I214" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="J214" s="6" t="inlineStr">
         <is>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -1,21 +1,25 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
-  <sheets>
-    <sheet state="visible" name="Resumo do Projeto" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Visão Geral das Sprints" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Backlog de Sprints" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Legenda" sheetId="4" r:id="rId8"/>
-  </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Backlog de Sprints'!$A$1:$K$132</definedName>
-  </definedNames>
-  <calcPr/>
-</workbook>
+<file path=xl\drawings\drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\drawings\drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl\drawings\drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl\drawings\drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl\persons\person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="432">
   <si>
     <t>Planejamento de Sprints</t>
@@ -1316,7 +1320,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <fonts count="7">
     <font>
@@ -1439,27 +1443,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
@@ -1653,7 +1637,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet state="visible" name="Resumo do Projeto" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Visão Geral das Sprints" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Backlog de Sprints" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Legenda" sheetId="4" r:id="rId8"/>
+  </sheets>
+  <definedNames>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Backlog de Sprints'!$A$1:$K$132</definedName>
+  </definedNames>
+  <calcPr/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -2908,7 +2908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -4948,7 +4948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J216" s="6" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I217" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J217" s="6" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J218" s="6" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I219" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J219" s="6" t="inlineStr">
@@ -15474,7 +15474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>

--- a/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
+++ b/docs/Sprints_Sistema_Gestao_Empresarial_Financeira.xlsx
@@ -14347,7 +14347,7 @@
       </c>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J220" s="6" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J221" s="6" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J222" s="6" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="I223" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J224" s="6" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="I225" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="I226" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Fazer</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
       <c r="J226" s="6" t="inlineStr">
